--- a/docs/legal-acts/export/EU 2025-1942.xlsx
+++ b/docs/legal-acts/export/EU 2025-1942.xlsx
@@ -473,7 +473,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21 18:24</t>
+          <t>2026-10-21 18:31</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
@@ -2387,7 +2387,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
@@ -2480,7 +2480,7 @@
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
@@ -2573,7 +2573,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
@@ -2852,7 +2852,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
@@ -2945,7 +2945,7 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
@@ -3224,7 +3224,7 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
@@ -3317,7 +3317,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
@@ -3410,7 +3410,7 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
@@ -3503,7 +3503,7 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
@@ -3596,7 +3596,7 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -3689,7 +3689,7 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
@@ -3875,7 +3875,7 @@
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -4061,7 +4061,7 @@
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
@@ -4619,7 +4619,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
@@ -4712,7 +4712,7 @@
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
@@ -4805,7 +4805,7 @@
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G47" s="3" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="F48" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G48" s="3" t="inlineStr">
@@ -5084,7 +5084,7 @@
       </c>
       <c r="F49" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G49" s="3" t="inlineStr">
@@ -5177,7 +5177,7 @@
       </c>
       <c r="F50" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G50" s="3" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="F51" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G51" s="3" t="inlineStr">
@@ -5363,7 +5363,7 @@
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G52" s="3" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G53" s="3" t="inlineStr">
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G54" s="3" t="inlineStr">
@@ -5642,7 +5642,7 @@
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G55" s="3" t="inlineStr">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G56" s="3" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G57" s="3" t="inlineStr">
@@ -5921,7 +5921,7 @@
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G58" s="3" t="inlineStr">
@@ -6014,7 +6014,7 @@
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G59" s="3" t="inlineStr">
@@ -6107,7 +6107,7 @@
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G60" s="3" t="inlineStr">
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G61" s="3" t="inlineStr">
@@ -6293,7 +6293,7 @@
       </c>
       <c r="F62" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G62" s="3" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="F63" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G63" s="3" t="inlineStr">
@@ -6479,7 +6479,7 @@
       </c>
       <c r="F64" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G64" s="3" t="inlineStr">
@@ -6572,7 +6572,7 @@
       </c>
       <c r="F65" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G65" s="3" t="inlineStr">
@@ -6665,7 +6665,7 @@
       </c>
       <c r="F66" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G66" s="3" t="inlineStr">
@@ -6758,7 +6758,7 @@
       </c>
       <c r="F67" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G67" s="3" t="inlineStr">
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F68" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G68" s="3" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="F69" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G69" s="3" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="F70" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G70" s="3" t="inlineStr">
@@ -7130,7 +7130,7 @@
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G71" s="3" t="inlineStr">
@@ -7223,7 +7223,7 @@
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G72" s="3" t="inlineStr">
@@ -7316,7 +7316,7 @@
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G73" s="3" t="inlineStr">
@@ -7409,7 +7409,7 @@
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G74" s="3" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F75" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G75" s="3" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="F76" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G76" s="3" t="inlineStr">
@@ -7688,7 +7688,7 @@
       </c>
       <c r="F77" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G77" s="3" t="inlineStr">
@@ -7781,7 +7781,7 @@
       </c>
       <c r="F78" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G78" s="3" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F79" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G79" s="3" t="inlineStr">
@@ -7967,7 +7967,7 @@
       </c>
       <c r="F80" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G80" s="3" t="inlineStr">
@@ -8060,7 +8060,7 @@
       </c>
       <c r="F81" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G81" s="3" t="inlineStr">
@@ -8153,7 +8153,7 @@
       </c>
       <c r="F82" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G82" s="3" t="inlineStr">
@@ -8246,7 +8246,7 @@
       </c>
       <c r="F83" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G83" s="3" t="inlineStr">
@@ -8339,7 +8339,7 @@
       </c>
       <c r="F84" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G84" s="3" t="inlineStr">
@@ -8432,7 +8432,7 @@
       </c>
       <c r="F85" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G85" s="3" t="inlineStr">
@@ -8525,7 +8525,7 @@
       </c>
       <c r="F86" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G86" s="3" t="inlineStr">
@@ -8618,7 +8618,7 @@
       </c>
       <c r="F87" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G87" s="3" t="inlineStr">
@@ -8711,7 +8711,7 @@
       </c>
       <c r="F88" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G88" s="3" t="inlineStr">
@@ -8804,7 +8804,7 @@
       </c>
       <c r="F89" s="3" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Article</t>
         </is>
       </c>
       <c r="G89" s="3" t="inlineStr">
